--- a/backtest_runs/20260410_193731/by_symbol/SAPT/SAPT.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SAPT/SAPT.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-780</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>99220</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>102243.28</v>
@@ -1231,7 +1231,7 @@
         <v>-1035.059999999999</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>101208.22</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>101208.22</v>
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>101208.22</v>
@@ -1369,7 +1369,7 @@
         <v>-4321.19999999999</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>96887.02</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>106329.7</v>
